--- a/data/employees/EMP014/AST-EMP014-06.xlsx
+++ b/data/employees/EMP014/AST-EMP014-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Productivity Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,199 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shift Productivity Report - Morgan Smith (Operations)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Morgan Smith | Role: Specialist | Location: Austin | Date: 2025-01-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>61</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>EMP014</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Lead A</t>
+          <t>Ast Emp014 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>Mentoring</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96</v>
+        <v>64</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>EMP014</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Lead B</t>
+          <t>Ast Emp014 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
+        <v>68</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>EMP014</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead C</t>
+          <t>Ast Emp014 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>EMP014</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead D</t>
+          <t>Ast Emp014 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G8" t="n">
-        <v>96.8</v>
+        <v>98</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>89</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>64</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>66</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>84</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>86</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>70</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>91</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>97</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>83</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>96</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>94</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>86</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>61</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>80</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp014 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>66</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP014</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP014 contributes to ast emp014 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>